--- a/cv_data/cv_entries.xlsx
+++ b/cv_data/cv_entries.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/090f7abe46c7f02e/GitHub/ccl_cv/cv_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{5E3E9FBA-CDAA-4D6C-8D19-28B232D6AF4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E829ADBF-B46F-4F85-8E24-0FC964F3282A}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{5E3E9FBA-CDAA-4D6C-8D19-28B232D6AF4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9727EDEA-264D-4298-BC6B-3FB98EA3F465}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{1BC556AC-FD23-42AD-A032-D140D4FFE02B}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="325">
   <si>
     <t>type</t>
   </si>
@@ -967,6 +967,39 @@
   </si>
   <si>
     <t>British Journal of Criminology</t>
+  </si>
+  <si>
+    <t>funding</t>
+  </si>
+  <si>
+    <t>Co-Investigator: Has the ‘Gun Show Loophole’ Been Closed, and of What Consequence for Gun Transactions and Violence?</t>
+  </si>
+  <si>
+    <t>$271,113</t>
+  </si>
+  <si>
+    <t>Co-PI: Disorder on Light Rail</t>
+  </si>
+  <si>
+    <t>Arnold Ventures. PI: Dave Kirk (University of Pennsylvania)</t>
+  </si>
+  <si>
+    <t>Sound Transit (Seattle, WA). Other Pis: Kyle Crowder and Nathalie Williams (University of Washington)</t>
+  </si>
+  <si>
+    <t>$4,445,968</t>
+  </si>
+  <si>
+    <t>Journal of Epidemiology &amp; Community Health</t>
+  </si>
+  <si>
+    <t>Differential social organization and cultural heterogeneity</t>
+  </si>
+  <si>
+    <t>*European Society of Criminology Annual Meeting*, Warsaw, PL</t>
+  </si>
+  <si>
+    <t>https://clanfear.github.io/ESC_2026/slides.html</t>
   </si>
 </sst>
 </file>
@@ -1364,7 +1397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2160BC3-6F18-4DB0-8375-6EA2E4BCFED4}">
-  <dimension ref="A1:H156"/>
+  <dimension ref="A1:H160"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.85546875" customWidth="1"/>
@@ -3858,6 +3891,74 @@
       </c>
       <c r="B156" t="s">
         <v>313</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>314</v>
+      </c>
+      <c r="B157" t="s">
+        <v>315</v>
+      </c>
+      <c r="C157" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="D157" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="E157" t="s">
+        <v>318</v>
+      </c>
+      <c r="F157" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>314</v>
+      </c>
+      <c r="B158" t="s">
+        <v>317</v>
+      </c>
+      <c r="C158" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="D158" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E158" t="s">
+        <v>319</v>
+      </c>
+      <c r="F158" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>69</v>
+      </c>
+      <c r="B159" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>8</v>
+      </c>
+      <c r="B160" t="s">
+        <v>322</v>
+      </c>
+      <c r="C160" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="E160" t="s">
+        <v>323</v>
+      </c>
+      <c r="G160" s="1">
+        <v>46276</v>
+      </c>
+      <c r="H160" s="2" t="s">
+        <v>324</v>
       </c>
     </row>
   </sheetData>
@@ -3882,8 +3983,9 @@
     <hyperlink ref="H141" r:id="rId17" xr:uid="{4DFB1F65-9DA4-4605-81E1-2FC00769EF0A}"/>
     <hyperlink ref="H147" r:id="rId18" xr:uid="{E204F4EF-E996-4D19-B6F3-679BA3B88CEB}"/>
     <hyperlink ref="H149" r:id="rId19" xr:uid="{C8F5A46F-F604-4371-989F-066614572D5D}"/>
+    <hyperlink ref="H160" r:id="rId20" xr:uid="{B673B375-AC6F-4A27-AED7-EF90EDEBFD5C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId20"/>
+  <pageSetup orientation="portrait" r:id="rId21"/>
 </worksheet>
 </file>
--- a/cv_data/cv_entries.xlsx
+++ b/cv_data/cv_entries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/090f7abe46c7f02e/GitHub/ccl_cv/cv_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{5E3E9FBA-CDAA-4D6C-8D19-28B232D6AF4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9727EDEA-264D-4298-BC6B-3FB98EA3F465}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="13_ncr:1_{5E3E9FBA-CDAA-4D6C-8D19-28B232D6AF4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{636F78C7-F4CE-42E1-A756-70BD77685302}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{1BC556AC-FD23-42AD-A032-D140D4FFE02B}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="325">
   <si>
     <t>type</t>
   </si>
@@ -858,9 +858,6 @@
     <t>Did closing the gun show loophole actually work?</t>
   </si>
   <si>
-    <t>Morven Brown</t>
-  </si>
-  <si>
     <t>John Hall</t>
   </si>
   <si>
@@ -1000,6 +997,9 @@
   </si>
   <si>
     <t>https://clanfear.github.io/ESC_2026/slides.html</t>
+  </si>
+  <si>
+    <t>Crime Prevention and Community Safety</t>
   </si>
 </sst>
 </file>
@@ -2568,7 +2568,7 @@
         <v>134</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E68" t="s">
         <v>138</v>
@@ -2630,7 +2630,7 @@
         <v>150</v>
       </c>
       <c r="F72" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H72" t="s">
         <v>153</v>
@@ -2653,7 +2653,7 @@
         <v>150</v>
       </c>
       <c r="F73" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H73" t="s">
         <v>152</v>
@@ -2861,7 +2861,7 @@
         <v>44</v>
       </c>
       <c r="B87" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C87" s="5" t="s">
         <v>158</v>
@@ -2895,16 +2895,16 @@
         <v>44</v>
       </c>
       <c r="B89" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D89" s="5" t="s">
         <v>53</v>
       </c>
       <c r="E89" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
@@ -3350,7 +3350,7 @@
         <v>44</v>
       </c>
       <c r="B120" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C120" s="5" t="s">
         <v>241</v>
@@ -3537,7 +3537,7 @@
         <v>8</v>
       </c>
       <c r="B134" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C134" s="5" t="s">
         <v>241</v>
@@ -3574,19 +3574,10 @@
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>163</v>
+        <v>69</v>
       </c>
       <c r="B136" t="s">
-        <v>277</v>
-      </c>
-      <c r="D136" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E136" t="s">
-        <v>150</v>
-      </c>
-      <c r="F136" t="s">
-        <v>220</v>
+        <v>324</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
@@ -3594,7 +3585,7 @@
         <v>163</v>
       </c>
       <c r="B137" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D137" s="5" t="s">
         <v>53</v>
@@ -3611,13 +3602,13 @@
         <v>24</v>
       </c>
       <c r="B138" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C138" s="5" t="s">
         <v>241</v>
       </c>
       <c r="E138" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
@@ -3625,7 +3616,7 @@
         <v>44</v>
       </c>
       <c r="B139" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C139" s="5" t="s">
         <v>241</v>
@@ -3642,7 +3633,7 @@
         <v>47</v>
       </c>
       <c r="B140" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C140" s="5" t="s">
         <v>134</v>
@@ -3654,10 +3645,10 @@
         <v>150</v>
       </c>
       <c r="F140" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
@@ -3665,7 +3656,7 @@
         <v>47</v>
       </c>
       <c r="B141" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C141" s="5" t="s">
         <v>241</v>
@@ -3677,7 +3668,7 @@
         <v>49</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -3685,7 +3676,7 @@
         <v>44</v>
       </c>
       <c r="B142" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C142" s="5" t="s">
         <v>241</v>
@@ -3702,7 +3693,7 @@
         <v>44</v>
       </c>
       <c r="B143" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C143" s="5" t="s">
         <v>241</v>
@@ -3711,7 +3702,7 @@
         <v>53</v>
       </c>
       <c r="E143" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
@@ -3719,7 +3710,7 @@
         <v>69</v>
       </c>
       <c r="B144" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
@@ -3727,7 +3718,7 @@
         <v>69</v>
       </c>
       <c r="B145" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
@@ -3735,10 +3726,10 @@
         <v>129</v>
       </c>
       <c r="B146" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D146" s="5" t="s">
         <v>53</v>
@@ -3752,10 +3743,10 @@
         <v>8</v>
       </c>
       <c r="B147" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E147" t="s">
         <v>138</v>
@@ -3764,7 +3755,7 @@
         <v>46057</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
@@ -3775,7 +3766,7 @@
         <v>212</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E148" t="s">
         <v>113</v>
@@ -3784,7 +3775,7 @@
         <v>46127</v>
       </c>
       <c r="H148" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -3792,19 +3783,19 @@
         <v>8</v>
       </c>
       <c r="B149" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E149" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G149" s="1">
         <v>46149</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
@@ -3812,19 +3803,19 @@
         <v>8</v>
       </c>
       <c r="B150" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E150" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G150" s="1">
         <v>46104</v>
       </c>
       <c r="H150" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
@@ -3832,7 +3823,7 @@
         <v>69</v>
       </c>
       <c r="B151" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
@@ -3840,13 +3831,13 @@
         <v>8</v>
       </c>
       <c r="B152" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E152" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G152" s="1">
         <v>46140</v>
@@ -3857,7 +3848,7 @@
         <v>69</v>
       </c>
       <c r="B153" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
@@ -3865,7 +3856,7 @@
         <v>69</v>
       </c>
       <c r="B154" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
@@ -3873,7 +3864,7 @@
         <v>163</v>
       </c>
       <c r="B155" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D155" s="5" t="s">
         <v>53</v>
@@ -3890,35 +3881,35 @@
         <v>69</v>
       </c>
       <c r="B156" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
+        <v>313</v>
+      </c>
+      <c r="B157" t="s">
         <v>314</v>
-      </c>
-      <c r="B157" t="s">
-        <v>315</v>
       </c>
       <c r="C157" s="5" t="s">
         <v>241</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E157" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F157" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B158" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C158" s="5" t="s">
         <v>196</v>
@@ -3927,10 +3918,10 @@
         <v>53</v>
       </c>
       <c r="E158" t="s">
+        <v>318</v>
+      </c>
+      <c r="F158" t="s">
         <v>319</v>
-      </c>
-      <c r="F158" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -3938,7 +3929,7 @@
         <v>69</v>
       </c>
       <c r="B159" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -3946,19 +3937,19 @@
         <v>8</v>
       </c>
       <c r="B160" t="s">
+        <v>321</v>
+      </c>
+      <c r="C160" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="E160" t="s">
         <v>322</v>
-      </c>
-      <c r="C160" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="E160" t="s">
-        <v>323</v>
       </c>
       <c r="G160" s="1">
         <v>46276</v>
       </c>
       <c r="H160" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>

--- a/cv_data/cv_entries.xlsx
+++ b/cv_data/cv_entries.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/090f7abe46c7f02e/GitHub/ccl_cv/cv_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="13_ncr:1_{5E3E9FBA-CDAA-4D6C-8D19-28B232D6AF4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{636F78C7-F4CE-42E1-A756-70BD77685302}"/>
+  <xr:revisionPtr revIDLastSave="50" documentId="13_ncr:1_{5E3E9FBA-CDAA-4D6C-8D19-28B232D6AF4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{787C3D84-8C9C-4333-B05A-FF70E4289954}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{1BC556AC-FD23-42AD-A032-D140D4FFE02B}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="326">
   <si>
     <t>type</t>
   </si>
@@ -897,9 +897,6 @@
     <t>Management Committee</t>
   </si>
   <si>
-    <t>MPhil Program Director</t>
-  </si>
-  <si>
     <t>Cambridge Research Methods (CaRM), University of Cambridge</t>
   </si>
   <si>
@@ -1000,6 +997,12 @@
   </si>
   <si>
     <t>Crime Prevention and Community Safety</t>
+  </si>
+  <si>
+    <t>Science Advances</t>
+  </si>
+  <si>
+    <t>MPhil Programme Director</t>
   </si>
 </sst>
 </file>
@@ -1397,7 +1400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2160BC3-6F18-4DB0-8375-6EA2E4BCFED4}">
-  <dimension ref="A1:H160"/>
+  <dimension ref="A1:H161"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.85546875" customWidth="1"/>
@@ -2568,7 +2571,7 @@
         <v>134</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E68" t="s">
         <v>138</v>
@@ -2895,16 +2898,16 @@
         <v>44</v>
       </c>
       <c r="B89" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D89" s="5" t="s">
         <v>53</v>
       </c>
       <c r="E89" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
@@ -3350,7 +3353,7 @@
         <v>44</v>
       </c>
       <c r="B120" t="s">
-        <v>290</v>
+        <v>325</v>
       </c>
       <c r="C120" s="5" t="s">
         <v>241</v>
@@ -3577,7 +3580,7 @@
         <v>69</v>
       </c>
       <c r="B136" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
@@ -3702,7 +3705,7 @@
         <v>53</v>
       </c>
       <c r="E143" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
@@ -3710,7 +3713,7 @@
         <v>69</v>
       </c>
       <c r="B144" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
@@ -3718,7 +3721,7 @@
         <v>69</v>
       </c>
       <c r="B145" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
@@ -3726,10 +3729,10 @@
         <v>129</v>
       </c>
       <c r="B146" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D146" s="5" t="s">
         <v>53</v>
@@ -3743,10 +3746,10 @@
         <v>8</v>
       </c>
       <c r="B147" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E147" t="s">
         <v>138</v>
@@ -3755,7 +3758,7 @@
         <v>46057</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
@@ -3766,7 +3769,7 @@
         <v>212</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E148" t="s">
         <v>113</v>
@@ -3775,7 +3778,7 @@
         <v>46127</v>
       </c>
       <c r="H148" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -3783,19 +3786,19 @@
         <v>8</v>
       </c>
       <c r="B149" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E149" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G149" s="1">
         <v>46149</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
@@ -3803,19 +3806,19 @@
         <v>8</v>
       </c>
       <c r="B150" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E150" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G150" s="1">
         <v>46104</v>
       </c>
       <c r="H150" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
@@ -3823,7 +3826,7 @@
         <v>69</v>
       </c>
       <c r="B151" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
@@ -3831,13 +3834,13 @@
         <v>8</v>
       </c>
       <c r="B152" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E152" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G152" s="1">
         <v>46140</v>
@@ -3848,7 +3851,7 @@
         <v>69</v>
       </c>
       <c r="B153" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
@@ -3856,7 +3859,7 @@
         <v>69</v>
       </c>
       <c r="B154" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
@@ -3864,7 +3867,7 @@
         <v>163</v>
       </c>
       <c r="B155" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D155" s="5" t="s">
         <v>53</v>
@@ -3881,35 +3884,35 @@
         <v>69</v>
       </c>
       <c r="B156" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
+        <v>312</v>
+      </c>
+      <c r="B157" t="s">
         <v>313</v>
-      </c>
-      <c r="B157" t="s">
-        <v>314</v>
       </c>
       <c r="C157" s="5" t="s">
         <v>241</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E157" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F157" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B158" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C158" s="5" t="s">
         <v>196</v>
@@ -3918,10 +3921,10 @@
         <v>53</v>
       </c>
       <c r="E158" t="s">
+        <v>317</v>
+      </c>
+      <c r="F158" t="s">
         <v>318</v>
-      </c>
-      <c r="F158" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -3929,7 +3932,7 @@
         <v>69</v>
       </c>
       <c r="B159" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -3937,19 +3940,27 @@
         <v>8</v>
       </c>
       <c r="B160" t="s">
+        <v>320</v>
+      </c>
+      <c r="C160" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="E160" t="s">
         <v>321</v>
-      </c>
-      <c r="C160" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="E160" t="s">
-        <v>322</v>
       </c>
       <c r="G160" s="1">
         <v>46276</v>
       </c>
       <c r="H160" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>69</v>
+      </c>
+      <c r="B161" t="s">
+        <v>324</v>
       </c>
     </row>
   </sheetData>
